--- a/data/현월/서비스 리드타임 현황.xlsx
+++ b/data/현월/서비스 리드타임 현황.xlsx
@@ -675,46 +675,46 @@
         </is>
       </c>
       <c r="G2" s="14" t="n">
-        <v>394.0</v>
+        <v>465.0</v>
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>219.26</t>
+          <t>224.65</t>
         </is>
       </c>
       <c r="I2" s="14" t="inlineStr">
         <is>
-          <t>198.14</t>
+          <t>203.90</t>
         </is>
       </c>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="K2" s="14" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="L2" s="14" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="M2" s="14" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.61</t>
         </is>
       </c>
       <c r="N2" s="14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="O2" s="14" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>30.79</t>
         </is>
       </c>
     </row>
@@ -746,21 +746,21 @@
         </is>
       </c>
       <c r="G3" s="14" t="n">
-        <v>162.0</v>
+        <v>187.0</v>
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>90.65</t>
+          <t>94.75</t>
         </is>
       </c>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>88.49</t>
         </is>
       </c>
       <c r="J3" s="14" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="K3" s="14" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.10</t>
         </is>
       </c>
     </row>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="G4" s="14" t="n">
-        <v>18.0</v>
+        <v>24.0</v>
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>123.59</t>
+          <t>157.62</t>
         </is>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
-          <t>107.43</t>
+          <t>137.60</t>
         </is>
       </c>
       <c r="J4" s="14" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="L4" s="14" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="M4" s="14" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="N4" s="14" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="O4" s="14" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>22.05</t>
         </is>
       </c>
     </row>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>271.91</t>
+          <t>257.69</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>219.89</t>
+          <t>207.81</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -959,16 +959,16 @@
         </is>
       </c>
       <c r="G6" s="14" t="n">
-        <v>94.0</v>
+        <v>117.0</v>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>368.35</t>
+          <t>378.69</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>363.02</t>
+          <t>374.01</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
@@ -983,22 +983,22 @@
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.84</t>
         </is>
       </c>
     </row>
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="G8" s="14" t="n">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>324.83</t>
+          <t>332.30</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>281.67</t>
+          <t>289.40</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>33.27</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
@@ -1172,16 +1172,16 @@
         </is>
       </c>
       <c r="G9" s="14" t="n">
-        <v>38.0</v>
+        <v>48.0</v>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>137.54</t>
+          <t>126.40</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="J9" s="14" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="M9" s="14" t="inlineStr">
         <is>
-          <t>99.17</t>
+          <t>91.20</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>267.45</t>
+          <t>232.37</t>
         </is>
       </c>
     </row>
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="G10" s="14" t="n">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>279.09</t>
+          <t>294.41</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>267.30</t>
+          <t>283.15</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="N10" s="14" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -1314,46 +1314,46 @@
         </is>
       </c>
       <c r="G11" s="14" t="n">
-        <v>117.0</v>
+        <v>150.0</v>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>255.98</t>
+          <t>258.98</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>225.22</t>
+          <t>228.51</t>
         </is>
       </c>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="M11" s="14" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>8.76</t>
         </is>
       </c>
     </row>
@@ -1385,16 +1385,16 @@
         </is>
       </c>
       <c r="G12" s="14" t="n">
-        <v>68.0</v>
+        <v>86.0</v>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>149.57</t>
+          <t>141.73</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>124.13</t>
+          <t>120.05</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
@@ -1409,22 +1409,22 @@
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>21.83</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="N12" s="14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.88</t>
         </is>
       </c>
     </row>
@@ -1456,16 +1456,16 @@
         </is>
       </c>
       <c r="G13" s="14" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>187.00</t>
+          <t>178.29</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>124.86</t>
+          <t>123.99</t>
         </is>
       </c>
       <c r="J13" s="14" t="inlineStr">
@@ -1475,22 +1475,22 @@
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>30.12</t>
         </is>
       </c>
       <c r="M13" s="14" t="inlineStr">
         <is>
-          <t>27.09</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
@@ -1527,46 +1527,46 @@
         </is>
       </c>
       <c r="G14" s="14" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>523.45</t>
+          <t>646.62</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>414.50</t>
+          <t>537.50</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>61.66</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>15.88</t>
         </is>
       </c>
     </row>
@@ -1598,21 +1598,21 @@
         </is>
       </c>
       <c r="G15" s="14" t="n">
-        <v>33.0</v>
+        <v>39.0</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>464.02</t>
+          <t>435.32</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>441.35</t>
+          <t>412.47</t>
         </is>
       </c>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
@@ -1622,22 +1622,22 @@
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="M15" s="14" t="inlineStr">
         <is>
-          <t>21.30</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.90</t>
         </is>
       </c>
     </row>
@@ -1740,16 +1740,16 @@
         </is>
       </c>
       <c r="G17" s="14" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>297.24</t>
+          <t>343.22</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>223.35</t>
+          <t>283.84</t>
         </is>
       </c>
       <c r="J17" s="14" t="inlineStr">
@@ -1759,17 +1759,17 @@
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="M17" s="14" t="inlineStr">
         <is>
-          <t>71.59</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="N17" s="14" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>3.64</t>
         </is>
       </c>
     </row>
@@ -1811,16 +1811,16 @@
         </is>
       </c>
       <c r="G18" s="14" t="n">
-        <v>126.0</v>
+        <v>151.0</v>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>159.68</t>
+          <t>170.34</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>140.36</t>
+          <t>152.75</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>15.22</t>
         </is>
       </c>
       <c r="N18" s="14" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.18</t>
         </is>
       </c>
     </row>
@@ -1882,16 +1882,16 @@
         </is>
       </c>
       <c r="G19" s="14" t="n">
-        <v>76.0</v>
+        <v>86.0</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>81.00</t>
+          <t>87.60</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>69.04</t>
+          <t>74.78</t>
         </is>
       </c>
       <c r="J19" s="14" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="M19" s="14" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -1953,16 +1953,16 @@
         </is>
       </c>
       <c r="G20" s="14" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>131.85</t>
+          <t>116.33</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>116.22</t>
+          <t>104.23</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.97</t>
         </is>
       </c>
     </row>
@@ -2095,16 +2095,16 @@
         </is>
       </c>
       <c r="G22" s="14" t="n">
-        <v>20.0</v>
+        <v>31.0</v>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>503.62</t>
+          <t>450.47</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>485.12</t>
+          <t>438.01</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
@@ -2114,17 +2114,17 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.93</t>
         </is>
       </c>
     </row>
@@ -2237,16 +2237,16 @@
         </is>
       </c>
       <c r="G24" s="14" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>129.55</t>
+          <t>131.36</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>79.23</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>49.04</t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
@@ -2308,16 +2308,16 @@
         </is>
       </c>
       <c r="G25" s="14" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="J25" s="14" t="inlineStr">
@@ -2327,17 +2327,17 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="M25" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="N25" s="14" t="inlineStr">
@@ -2379,46 +2379,46 @@
         </is>
       </c>
       <c r="G26" s="14" t="n">
-        <v>522.0</v>
+        <v>634.0</v>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>323.05</t>
+          <t>313.37</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>272.90</t>
+          <t>265.56</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="N26" s="14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>14.88</t>
         </is>
       </c>
     </row>
@@ -2450,21 +2450,21 @@
         </is>
       </c>
       <c r="G27" s="14" t="n">
-        <v>212.0</v>
+        <v>256.0</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>195.40</t>
+          <t>185.06</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>182.60</t>
+          <t>173.05</t>
         </is>
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="M27" s="14" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="N27" s="14" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>11.59</t>
         </is>
       </c>
     </row>
@@ -2521,36 +2521,36 @@
         </is>
       </c>
       <c r="G28" s="14" t="n">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>361.18</t>
+          <t>346.00</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>224.70</t>
+          <t>230.14</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>32.10</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>65.56</t>
         </is>
       </c>
       <c r="N28" s="14" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.23</t>
         </is>
       </c>
     </row>
@@ -2663,21 +2663,21 @@
         </is>
       </c>
       <c r="G30" s="14" t="n">
-        <v>137.0</v>
+        <v>161.0</v>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>461.53</t>
+          <t>457.61</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>439.45</t>
+          <t>437.34</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
@@ -2687,22 +2687,22 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="N30" s="14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>18.48</t>
         </is>
       </c>
     </row>
@@ -2734,16 +2734,16 @@
         </is>
       </c>
       <c r="G31" s="14" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>1067.87</t>
+          <t>1185.81</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>904.95</t>
+          <t>1023.31</t>
         </is>
       </c>
       <c r="J31" s="14" t="inlineStr">
@@ -2753,22 +2753,22 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>13.86</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
         <is>
-          <t>158.28</t>
+          <t>148.49</t>
         </is>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="O31" s="14" t="inlineStr">
@@ -2805,21 +2805,21 @@
         </is>
       </c>
       <c r="G32" s="14" t="n">
-        <v>43.0</v>
+        <v>57.0</v>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>350.34</t>
+          <t>341.15</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>255.95</t>
+          <t>236.97</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
@@ -2829,22 +2829,22 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>18.26</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>78.68</t>
         </is>
       </c>
       <c r="N32" s="14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="O32" s="14" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.34</t>
         </is>
       </c>
     </row>
@@ -2876,16 +2876,16 @@
         </is>
       </c>
       <c r="G33" s="14" t="n">
-        <v>42.0</v>
+        <v>56.0</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>204.65</t>
+          <t>182.59</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="J33" s="14" t="inlineStr">
@@ -2895,27 +2895,27 @@
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>79.76</t>
+          <t>69.18</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
         <is>
-          <t>87.35</t>
+          <t>76.16</t>
         </is>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="O33" s="14" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>27.12</t>
         </is>
       </c>
     </row>
@@ -2947,46 +2947,46 @@
         </is>
       </c>
       <c r="G34" s="14" t="n">
-        <v>22.0</v>
+        <v>26.0</v>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>453.33</t>
+          <t>436.70</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>431.85</t>
+          <t>416.54</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="O34" s="14" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>30.91</t>
         </is>
       </c>
     </row>
@@ -3018,16 +3018,16 @@
         </is>
       </c>
       <c r="G35" s="14" t="n">
-        <v>105.0</v>
+        <v>127.0</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>306.60</t>
+          <t>282.88</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>295.15</t>
+          <t>272.52</t>
         </is>
       </c>
       <c r="J35" s="14" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="N35" s="14" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O35" s="14" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>5.81</t>
         </is>
       </c>
     </row>
@@ -3089,16 +3089,16 @@
         </is>
       </c>
       <c r="G36" s="14" t="n">
-        <v>45.0</v>
+        <v>60.0</v>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>184.13</t>
+          <t>172.76</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>174.69</t>
+          <t>164.26</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="N36" s="14" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>6.57</t>
         </is>
       </c>
     </row>
@@ -3160,16 +3160,16 @@
         </is>
       </c>
       <c r="G37" s="14" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>326.40</t>
+          <t>290.78</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>305.65</t>
+          <t>272.53</t>
         </is>
       </c>
       <c r="J37" s="14" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="N37" s="14" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -3302,16 +3302,16 @@
         </is>
       </c>
       <c r="G39" s="14" t="n">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>463.63</t>
+          <t>449.88</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>462.14</t>
+          <t>448.34</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="N39" s="14" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="O39" s="14" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>6.17</t>
         </is>
       </c>
     </row>
@@ -3373,16 +3373,16 @@
         </is>
       </c>
       <c r="G40" s="14" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>424.93</t>
+          <t>420.88</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>385.65</t>
+          <t>387.35</t>
         </is>
       </c>
       <c r="J40" s="14" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="N40" s="14" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="O40" s="14" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.59</t>
         </is>
       </c>
     </row>
@@ -3444,16 +3444,16 @@
         </is>
       </c>
       <c r="G41" s="14" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>276.13</t>
+          <t>261.21</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>266.63</t>
+          <t>252.35</t>
         </is>
       </c>
       <c r="J41" s="14" t="inlineStr">
@@ -3463,17 +3463,17 @@
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="N41" s="14" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.06</t>
         </is>
       </c>
     </row>
